--- a/TestQuetions.xlsx
+++ b/TestQuetions.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Tegveer\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F7133BB-0F32-4AC1-8B6F-7B3B6DCFBFD9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E48E346-8FA3-4A67-BEF0-ABB4E955D721}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{B3C127FB-2A8F-452B-AF2E-E404EB9CD154}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="69">
   <si>
     <t>ID</t>
   </si>
@@ -48,44 +48,206 @@
     <t>Q001</t>
   </si>
   <si>
-    <t>Who developed Minecraft?</t>
-  </si>
-  <si>
     <t>B</t>
   </si>
   <si>
     <t>Q002</t>
   </si>
   <si>
-    <t>What is the largest planet?</t>
-  </si>
-  <si>
     <t>C</t>
   </si>
   <si>
     <t>Q003</t>
   </si>
   <si>
-    <t>Which company owns PlayStation?</t>
-  </si>
-  <si>
     <t>A</t>
   </si>
   <si>
     <t>Q004</t>
   </si>
   <si>
-    <t>Which year was GTA V released?</t>
-  </si>
-  <si>
-    <t>D</t>
+    <t>What is the greatest wonder in the world?</t>
+  </si>
+  <si>
+    <t>What makes a person truly wise?</t>
+  </si>
+  <si>
+    <t>What is the greatest treasure?</t>
+  </si>
+  <si>
+    <t>What is the best path to happiness?</t>
+  </si>
+  <si>
+    <t>Who is truly rich?</t>
+  </si>
+  <si>
+    <t>What is the greatest virtue?</t>
+  </si>
+  <si>
+    <t>what destroys a person's wisdom?</t>
+  </si>
+  <si>
+    <t>What gives a person true happiness?</t>
+  </si>
+  <si>
+    <t>What is the best weapon against danger?</t>
+  </si>
+  <si>
+    <t>What should you do when you don't know the answer?</t>
+  </si>
+  <si>
+    <t>What is more important than winning?</t>
+  </si>
+  <si>
+    <t>Why did Yudhishthira choose Nakula to be revived?</t>
+  </si>
+  <si>
+    <t>What is the best response to templation?</t>
+  </si>
+  <si>
+    <t>According to the story' what should guide our decisions?</t>
+  </si>
+  <si>
+    <t>What happens when a person acts without thinking?</t>
+  </si>
+  <si>
+    <t>What makes a person truly noble?</t>
+  </si>
+  <si>
+    <t>The Yaksha offes to bring only one brother back to life. What should Yudhishthira consider first?</t>
+  </si>
+  <si>
+    <t>Which action best represents Dharma?</t>
+  </si>
+  <si>
+    <t>What happens when a person is controlled by endless desire?</t>
+  </si>
+  <si>
+    <t>Which of these represents true happiness?</t>
+  </si>
+  <si>
+    <t>You have two friends who both need you help, but you can help only one. What should you do?</t>
+  </si>
+  <si>
+    <t>Would you follow Dharma even if your decision meant giving up something you deeply wanted?</t>
+  </si>
+  <si>
+    <t>in the Yaksha's test what is more imporant for making the right decision?</t>
+  </si>
+  <si>
+    <t>you can save only one person which choice best follows Dharma?</t>
+  </si>
+  <si>
+    <t>You discover that telling the truth will hurt someone you love. What do you do?</t>
+  </si>
+  <si>
+    <t>You receive unlimited wealth, but you will never feel satisfied. Do you accept it?</t>
+  </si>
+  <si>
+    <t>What matters most when making a difficult decision?</t>
+  </si>
+  <si>
+    <t>when faced with a difficult situation&lt; what is the wisest response?</t>
+  </si>
+  <si>
+    <t>Why is truth important when following Dharma?</t>
+  </si>
+  <si>
+    <t>If helping another person brings you no reward, what should Dharma encourage you to do?</t>
+  </si>
+  <si>
+    <t>Which path best respresents the lesson of Yudhidhthira"s test?</t>
+  </si>
+  <si>
+    <t>Q005</t>
+  </si>
+  <si>
+    <t>Q006</t>
+  </si>
+  <si>
+    <t>Q007</t>
+  </si>
+  <si>
+    <t>Q008</t>
+  </si>
+  <si>
+    <t>Q009</t>
+  </si>
+  <si>
+    <t>Q010</t>
+  </si>
+  <si>
+    <t>Q011</t>
+  </si>
+  <si>
+    <t>Q012</t>
+  </si>
+  <si>
+    <t>Q013</t>
+  </si>
+  <si>
+    <t>Q014</t>
+  </si>
+  <si>
+    <t>Q015</t>
+  </si>
+  <si>
+    <t>Q016</t>
+  </si>
+  <si>
+    <t>Q017</t>
+  </si>
+  <si>
+    <t>Q018</t>
+  </si>
+  <si>
+    <t>Q019</t>
+  </si>
+  <si>
+    <t>Q020</t>
+  </si>
+  <si>
+    <t>Q021</t>
+  </si>
+  <si>
+    <t>Q022</t>
+  </si>
+  <si>
+    <t>Q023</t>
+  </si>
+  <si>
+    <t>Q024</t>
+  </si>
+  <si>
+    <t>Q025</t>
+  </si>
+  <si>
+    <t>Q026</t>
+  </si>
+  <si>
+    <t>Q027</t>
+  </si>
+  <si>
+    <t>Q028</t>
+  </si>
+  <si>
+    <t>Q029</t>
+  </si>
+  <si>
+    <t>Q030</t>
+  </si>
+  <si>
+    <t>Q031</t>
+  </si>
+  <si>
+    <t>Q032</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -101,6 +263,12 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -110,7 +278,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -118,17 +286,38 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFCCCCCC"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFCCCCCC"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFCCCCCC"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FFCCCCCC"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -444,15 +633,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{509EE961-F5F8-4BC8-9BA2-F503EB653B1E}">
-  <dimension ref="A1:C5"/>
+  <dimension ref="A1:C33"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="16.88671875" customWidth="1"/>
-    <col min="2" max="2" width="21.6640625" customWidth="1"/>
+    <col min="2" max="2" width="36.21875" customWidth="1"/>
     <col min="3" max="3" width="26.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -463,51 +652,360 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="72" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="C2" s="2" t="s">
+      <c r="B2" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="2" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="3" spans="1:3" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A3" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="B4" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A10" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C10" s="4" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="72" x14ac:dyDescent="0.3">
-      <c r="A4" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="B4" s="2" t="s">
+    <row r="11" spans="1:3" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A11" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A12" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A13" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A14" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A15" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="C15" s="4" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A16" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C16" s="4" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A17" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="C17" s="4" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A18" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B18" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C4" s="2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A5" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>14</v>
+      <c r="C18" s="4" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" ht="43.8" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A19" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C19" s="4" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A20" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="C20" s="4" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A21" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="C21" s="4" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A22" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="C22" s="4" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" ht="43.8" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A23" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="C23" s="4" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" ht="43.8" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A24" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C24" s="4" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A25" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C25" s="4" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A26" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="C26" s="4" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A27" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="C27" s="4" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A28" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="C28" s="4" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A29" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="C29" s="4" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A30" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="C30" s="4" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A31" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="B31" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="C31" s="4" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" ht="43.8" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A32" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="B32" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="C32" s="4" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A33" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="B33" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="C33" s="4" t="s">
+        <v>6</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>